--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra400c4b89e9a449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e95d816205468e"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96e95d816205468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R206ad31bc4bc4641"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R206ad31bc4bc4641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fa049da35944ff8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fa049da35944ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90054b3884a04c09"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90054b3884a04c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R366bf847941a4ddc"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R366bf847941a4ddc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5cb8260ee379431e"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5cb8260ee379431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb94558b153b44bc7"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>
